--- a/artfynd/A 19331-2024 artfynd.xlsx
+++ b/artfynd/A 19331-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>55773745</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528167.7629537772</v>
+        <v>528168</v>
       </c>
       <c r="R2" t="n">
-        <v>7177069.523007786</v>
+        <v>7177070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-07-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-07-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -814,37 +799,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119413538</v>
+        <v>119413536</v>
       </c>
       <c r="B3" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -857,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528298</v>
+        <v>528451</v>
       </c>
       <c r="R3" t="n">
-        <v>7176962</v>
+        <v>7177031</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -960,15 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119413583</v>
+        <v>119413540</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,34 +951,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528306</v>
+        <v>528298</v>
       </c>
       <c r="R4" t="n">
-        <v>7177016</v>
+        <v>7176962</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1035,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1045,7 +1023,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,8 +1037,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1072,15 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119413558</v>
+        <v>119413543</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,34 +1092,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528029</v>
+        <v>528286</v>
       </c>
       <c r="R5" t="n">
-        <v>7177243</v>
+        <v>7176921</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1147,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1157,7 +1164,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,8 +1178,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1184,50 +1222,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119413568</v>
+        <v>119413547</v>
       </c>
       <c r="B6" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528208</v>
+        <v>528091</v>
       </c>
       <c r="R6" t="n">
-        <v>7177000</v>
+        <v>7176972</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1259,7 +1295,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1305,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1283,8 +1319,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1301,37 +1363,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119413585</v>
+        <v>119413563</v>
       </c>
       <c r="B7" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1344,10 +1401,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528279</v>
+        <v>528191</v>
       </c>
       <c r="R7" t="n">
-        <v>7177023</v>
+        <v>7177051</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1379,7 +1436,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,12 +1446,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på 2 levande sälgar</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,15 +1504,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119413592</v>
+        <v>119413564</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,31 +1515,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1495,10 +1542,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528318</v>
+        <v>528201</v>
       </c>
       <c r="R8" t="n">
-        <v>7177094</v>
+        <v>7177052</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1530,7 +1577,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1540,12 +1587,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,8 +1601,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1572,15 +1645,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119413559</v>
+        <v>119413566</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,34 +1656,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528112</v>
+        <v>528208</v>
       </c>
       <c r="R9" t="n">
-        <v>7177228</v>
+        <v>7177034</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1647,7 +1718,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1657,7 +1728,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,8 +1742,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1684,15 +1786,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119413552</v>
+        <v>119413569</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,21 +1797,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1727,10 +1824,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527999</v>
+        <v>528208</v>
       </c>
       <c r="R10" t="n">
-        <v>7177037</v>
+        <v>7177000</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1762,7 +1859,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1772,7 +1869,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1830,15 +1927,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119413564</v>
+        <v>119413572</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,10 +1965,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528201</v>
+        <v>528247</v>
       </c>
       <c r="R11" t="n">
-        <v>7177052</v>
+        <v>7176979</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1908,7 +2000,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1918,12 +2010,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1976,15 +2063,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119413563</v>
+        <v>119413573</v>
       </c>
       <c r="B12" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2019,10 +2101,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528191</v>
+        <v>528252</v>
       </c>
       <c r="R12" t="n">
-        <v>7177051</v>
+        <v>7176983</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2054,7 +2136,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2064,12 +2146,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på 2 levande sälgar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2122,37 +2204,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119413535</v>
+        <v>119413577</v>
       </c>
       <c r="B13" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2165,10 +2242,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528451</v>
+        <v>528294</v>
       </c>
       <c r="R13" t="n">
-        <v>7177031</v>
+        <v>7176973</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2200,7 +2277,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2210,7 +2287,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2268,15 +2345,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119413556</v>
+        <v>119413580</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2284,34 +2356,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528005</v>
+        <v>528327</v>
       </c>
       <c r="R14" t="n">
-        <v>7177137</v>
+        <v>7176985</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2343,7 +2418,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2353,7 +2428,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2362,8 +2442,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2380,15 +2486,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119413545</v>
+        <v>119413582</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,34 +2497,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528211</v>
+        <v>528318</v>
       </c>
       <c r="R15" t="n">
-        <v>7176960</v>
+        <v>7176985</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2455,7 +2559,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2465,7 +2569,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>på 2 levande sälgar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2474,8 +2583,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2492,15 +2627,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119413544</v>
+        <v>119413584</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2508,34 +2638,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528244</v>
+        <v>528279</v>
       </c>
       <c r="R16" t="n">
-        <v>7176878</v>
+        <v>7177023</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2567,7 +2700,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2577,7 +2710,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>på 2 levande sälgar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2586,8 +2724,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2604,15 +2768,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119413540</v>
+        <v>119413587</v>
       </c>
       <c r="B17" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2647,10 +2806,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528298</v>
+        <v>528268</v>
       </c>
       <c r="R17" t="n">
-        <v>7176962</v>
+        <v>7177062</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2682,7 +2841,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2692,7 +2851,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2750,37 +2909,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119413581</v>
+        <v>119413589</v>
       </c>
       <c r="B18" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2793,10 +2947,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528318</v>
+        <v>528278</v>
       </c>
       <c r="R18" t="n">
-        <v>7176985</v>
+        <v>7177059</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2828,7 +2982,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2838,12 +2992,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på 2 levande sälgar</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2896,37 +3050,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119413586</v>
+        <v>119413590</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2939,10 +3088,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528268</v>
+        <v>528287</v>
       </c>
       <c r="R19" t="n">
-        <v>7177062</v>
+        <v>7177049</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2974,7 +3123,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2984,7 +3133,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3042,15 +3191,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119413550</v>
+        <v>119413594</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,31 +3202,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3090,10 +3229,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528017</v>
+        <v>528309</v>
       </c>
       <c r="R20" t="n">
-        <v>7176978</v>
+        <v>7177102</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3125,7 +3264,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3135,12 +3274,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>gamla ringhack  död knäckt gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3149,8 +3288,34 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3167,53 +3332,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119413577</v>
+        <v>119413537</v>
       </c>
       <c r="B21" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528294</v>
+        <v>528363</v>
       </c>
       <c r="R21" t="n">
-        <v>7176973</v>
+        <v>7176955</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3245,7 +3402,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3255,12 +3412,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3269,34 +3421,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3313,53 +3439,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119413587</v>
+        <v>119413539</v>
       </c>
       <c r="B22" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528268</v>
+        <v>528298</v>
       </c>
       <c r="R22" t="n">
-        <v>7177062</v>
+        <v>7176962</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3391,7 +3509,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3401,7 +3519,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3415,34 +3533,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3459,53 +3551,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119413536</v>
+        <v>119413544</v>
       </c>
       <c r="B23" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528451</v>
+        <v>528244</v>
       </c>
       <c r="R23" t="n">
-        <v>7177031</v>
+        <v>7176878</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3537,7 +3621,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3547,12 +3631,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3561,34 +3640,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3605,53 +3658,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119413553</v>
+        <v>119413545</v>
       </c>
       <c r="B24" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527964</v>
+        <v>528211</v>
       </c>
       <c r="R24" t="n">
-        <v>7177111</v>
+        <v>7176960</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3683,7 +3728,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3693,7 +3738,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3702,34 +3747,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3746,53 +3765,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119413588</v>
+        <v>119413546</v>
       </c>
       <c r="B25" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528278</v>
+        <v>528130</v>
       </c>
       <c r="R25" t="n">
-        <v>7177059</v>
+        <v>7177013</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3824,7 +3835,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3834,12 +3845,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3848,34 +3854,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3892,19 +3872,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119413567</v>
+        <v>119413549</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3932,10 +3907,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528202</v>
+        <v>528034</v>
       </c>
       <c r="R26" t="n">
-        <v>7177014</v>
+        <v>7176967</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3967,7 +3942,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3977,7 +3952,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4004,19 +3979,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119413575</v>
+        <v>119413556</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -4044,10 +4014,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528264</v>
+        <v>528005</v>
       </c>
       <c r="R27" t="n">
-        <v>7176972</v>
+        <v>7177137</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -4079,7 +4049,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4089,7 +4059,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4116,19 +4086,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119413609</v>
+        <v>119413558</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -4156,10 +4121,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528430</v>
+        <v>528029</v>
       </c>
       <c r="R28" t="n">
-        <v>7177074</v>
+        <v>7177243</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4191,7 +4156,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4201,7 +4166,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4228,53 +4193,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119413557</v>
+        <v>119413559</v>
       </c>
       <c r="B29" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528012</v>
+        <v>528112</v>
       </c>
       <c r="R29" t="n">
-        <v>7177207</v>
+        <v>7177228</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4306,7 +4263,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4316,12 +4273,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4330,34 +4282,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4374,53 +4300,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119413566</v>
+        <v>119413567</v>
       </c>
       <c r="B30" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528208</v>
+        <v>528202</v>
       </c>
       <c r="R30" t="n">
-        <v>7177034</v>
+        <v>7177014</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4452,7 +4370,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4462,12 +4380,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>på död sälg</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4476,34 +4389,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4520,53 +4407,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119413589</v>
+        <v>119413570</v>
       </c>
       <c r="B31" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528278</v>
+        <v>528237</v>
       </c>
       <c r="R31" t="n">
-        <v>7177059</v>
+        <v>7176973</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4598,7 +4477,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4608,12 +4487,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4622,34 +4496,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4666,53 +4514,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119413590</v>
+        <v>119413575</v>
       </c>
       <c r="B32" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528287</v>
+        <v>528264</v>
       </c>
       <c r="R32" t="n">
-        <v>7177049</v>
+        <v>7176972</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4744,7 +4584,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4754,12 +4594,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4768,34 +4603,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4812,19 +4621,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119413579</v>
+        <v>119413576</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4852,10 +4656,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528327</v>
+        <v>528299</v>
       </c>
       <c r="R33" t="n">
-        <v>7176985</v>
+        <v>7176965</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4887,7 +4691,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4897,12 +4701,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4929,19 +4728,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119413601</v>
+        <v>119413579</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4969,10 +4763,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528310</v>
+        <v>528327</v>
       </c>
       <c r="R34" t="n">
-        <v>7177180</v>
+        <v>7176985</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -5004,7 +4798,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5014,7 +4808,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5041,58 +4840,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119413565</v>
+        <v>119413583</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528201</v>
+        <v>528306</v>
       </c>
       <c r="R35" t="n">
-        <v>7177036</v>
+        <v>7177016</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5124,7 +4910,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5134,12 +4920,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5166,53 +4947,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119413580</v>
+        <v>119413591</v>
       </c>
       <c r="B36" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528327</v>
+        <v>528309</v>
       </c>
       <c r="R36" t="n">
-        <v>7176985</v>
+        <v>7177076</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5244,7 +5017,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5254,12 +5027,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5268,34 +5036,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5312,53 +5054,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119413582</v>
+        <v>119413595</v>
       </c>
       <c r="B37" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528318</v>
+        <v>528303</v>
       </c>
       <c r="R37" t="n">
-        <v>7176985</v>
+        <v>7177102</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5390,7 +5124,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5400,12 +5134,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>på 2 levande sälgar</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5414,34 +5143,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5458,53 +5161,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119413543</v>
+        <v>119413597</v>
       </c>
       <c r="B38" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528286</v>
+        <v>528283</v>
       </c>
       <c r="R38" t="n">
-        <v>7176921</v>
+        <v>7177156</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5536,7 +5231,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5546,12 +5241,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5560,34 +5250,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5604,19 +5268,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119413576</v>
+        <v>119413599</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -5644,10 +5303,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528299</v>
+        <v>528314</v>
       </c>
       <c r="R39" t="n">
-        <v>7176965</v>
+        <v>7177133</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5679,7 +5338,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5689,7 +5348,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5716,19 +5375,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119413546</v>
+        <v>119413601</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5756,10 +5410,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528130</v>
+        <v>528310</v>
       </c>
       <c r="R40" t="n">
-        <v>7177013</v>
+        <v>7177180</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5791,7 +5445,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5801,7 +5455,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5828,53 +5482,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119413541</v>
+        <v>119413603</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528286</v>
+        <v>528335</v>
       </c>
       <c r="R41" t="n">
-        <v>7176921</v>
+        <v>7177074</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5906,7 +5552,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5916,12 +5562,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5930,34 +5571,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5974,19 +5589,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119413603</v>
+        <v>119413605</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -6014,7 +5624,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528335</v>
+        <v>528377</v>
       </c>
       <c r="R42" t="n">
         <v>7177074</v>
@@ -6049,7 +5659,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6059,7 +5669,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6086,19 +5696,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119413539</v>
+        <v>119413606</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -6126,10 +5731,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528298</v>
+        <v>528385</v>
       </c>
       <c r="R43" t="n">
-        <v>7176962</v>
+        <v>7177074</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6161,7 +5766,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6171,12 +5776,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6203,19 +5803,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119413537</v>
+        <v>119413608</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -6243,10 +5838,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528363</v>
+        <v>528412</v>
       </c>
       <c r="R44" t="n">
-        <v>7176955</v>
+        <v>7177074</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6278,7 +5873,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6288,7 +5883,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6315,53 +5910,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119413594</v>
+        <v>119413609</v>
       </c>
       <c r="B45" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528309</v>
+        <v>528430</v>
       </c>
       <c r="R45" t="n">
-        <v>7177102</v>
+        <v>7177074</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6393,7 +5980,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6403,12 +5990,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6417,34 +5999,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6461,19 +6017,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119413597</v>
+        <v>119413611</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -6501,10 +6052,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528283</v>
+        <v>528468</v>
       </c>
       <c r="R46" t="n">
-        <v>7177156</v>
+        <v>7177074</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6536,7 +6087,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6546,7 +6097,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6573,15 +6124,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119413591</v>
+        <v>119413541</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6589,34 +6135,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528309</v>
+        <v>528286</v>
       </c>
       <c r="R47" t="n">
-        <v>7177076</v>
+        <v>7176921</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6648,7 +6197,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6658,7 +6207,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6667,8 +6221,34 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6685,15 +6265,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119413599</v>
+        <v>119413552</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6701,34 +6276,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528314</v>
+        <v>527999</v>
       </c>
       <c r="R48" t="n">
-        <v>7177133</v>
+        <v>7177037</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6760,7 +6338,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6770,7 +6348,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6779,8 +6362,34 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6797,15 +6406,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119413560</v>
+        <v>119413562</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6813,31 +6417,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6845,10 +6444,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528201</v>
+        <v>528224</v>
       </c>
       <c r="R49" t="n">
-        <v>7177131</v>
+        <v>7177147</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6880,7 +6479,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6890,12 +6489,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>färska och gamla ringhack</t>
+          <t>på levande asp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6904,8 +6503,34 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6922,15 +6547,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119413596</v>
+        <v>119413578</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6938,31 +6558,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6970,10 +6585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528271</v>
+        <v>528327</v>
       </c>
       <c r="R50" t="n">
-        <v>7177121</v>
+        <v>7176985</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -7005,7 +6620,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7015,12 +6630,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>färska och gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7029,8 +6644,34 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7047,37 +6688,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119413584</v>
+        <v>119413586</v>
       </c>
       <c r="B51" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7090,10 +6726,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528279</v>
+        <v>528268</v>
       </c>
       <c r="R51" t="n">
-        <v>7177023</v>
+        <v>7177062</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7125,7 +6761,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7135,12 +6771,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>på 2 levande sälgar</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7193,37 +6829,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119413562</v>
+        <v>119413574</v>
       </c>
       <c r="B52" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7236,10 +6867,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528224</v>
+        <v>528251</v>
       </c>
       <c r="R52" t="n">
-        <v>7177147</v>
+        <v>7176983</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -7271,7 +6902,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7281,12 +6912,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>på levande asp</t>
+          <t>på 2 levande sälgar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7306,12 +6937,12 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -7321,7 +6952,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7339,15 +6970,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119413551</v>
+        <v>119413535</v>
       </c>
       <c r="B53" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7382,10 +7008,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528017</v>
+        <v>528451</v>
       </c>
       <c r="R53" t="n">
-        <v>7177026</v>
+        <v>7177031</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -7417,7 +7043,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7427,7 +7053,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7485,15 +7111,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119413561</v>
+        <v>119413538</v>
       </c>
       <c r="B54" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7528,10 +7149,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528211</v>
+        <v>528298</v>
       </c>
       <c r="R54" t="n">
-        <v>7177144</v>
+        <v>7176962</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7563,7 +7184,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7573,7 +7194,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7631,37 +7252,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119413547</v>
+        <v>119413542</v>
       </c>
       <c r="B55" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7674,10 +7290,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>528091</v>
+        <v>528286</v>
       </c>
       <c r="R55" t="n">
-        <v>7176972</v>
+        <v>7176921</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7709,7 +7325,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7719,7 +7335,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7777,50 +7393,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119413595</v>
+        <v>119413551</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>528303</v>
+        <v>528017</v>
       </c>
       <c r="R56" t="n">
-        <v>7177102</v>
+        <v>7177026</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7852,7 +7466,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7862,7 +7476,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7871,8 +7490,34 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7889,50 +7534,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119413611</v>
+        <v>119413553</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>528468</v>
+        <v>527964</v>
       </c>
       <c r="R57" t="n">
-        <v>7177074</v>
+        <v>7177111</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7964,7 +7607,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7974,7 +7617,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7983,8 +7626,34 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -8001,37 +7670,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119413578</v>
+        <v>119413554</v>
       </c>
       <c r="B58" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8044,10 +7708,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>528327</v>
+        <v>527974</v>
       </c>
       <c r="R58" t="n">
-        <v>7176985</v>
+        <v>7177116</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -8079,7 +7743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8089,7 +7753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8147,47 +7811,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119413598</v>
+        <v>119413557</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8195,10 +7849,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>528314</v>
+        <v>528012</v>
       </c>
       <c r="R59" t="n">
-        <v>7177133</v>
+        <v>7177207</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -8230,7 +7884,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8240,12 +7894,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8254,8 +7908,34 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -8272,15 +7952,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119413571</v>
+        <v>119413561</v>
       </c>
       <c r="B60" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8306,16 +7981,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>528247</v>
+        <v>528211</v>
       </c>
       <c r="R60" t="n">
-        <v>7176979</v>
+        <v>7177144</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -8347,7 +8025,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8357,7 +8035,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8366,8 +8049,34 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8384,43 +8093,35 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119413569</v>
+        <v>119413568</v>
       </c>
       <c r="B61" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
@@ -8486,34 +8187,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -8530,15 +8205,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119413542</v>
+        <v>119413571</v>
       </c>
       <c r="B62" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8564,19 +8234,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>528286</v>
+        <v>528247</v>
       </c>
       <c r="R62" t="n">
-        <v>7176921</v>
+        <v>7176979</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8608,7 +8275,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8618,12 +8285,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8632,34 +8294,8 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8676,15 +8312,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119413554</v>
+        <v>119413581</v>
       </c>
       <c r="B63" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8719,10 +8350,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527974</v>
+        <v>528318</v>
       </c>
       <c r="R63" t="n">
-        <v>7177116</v>
+        <v>7176985</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8754,7 +8385,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8764,12 +8395,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på 2 levande sälgar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8822,50 +8453,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119413570</v>
+        <v>119413585</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>528237</v>
+        <v>528279</v>
       </c>
       <c r="R64" t="n">
-        <v>7176973</v>
+        <v>7177023</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8897,7 +8526,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8907,7 +8536,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>på 2 levande sälgar</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8916,8 +8550,34 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8934,37 +8594,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119413572</v>
+        <v>119413588</v>
       </c>
       <c r="B65" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8977,10 +8632,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>528247</v>
+        <v>528278</v>
       </c>
       <c r="R65" t="n">
-        <v>7176979</v>
+        <v>7177059</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -9012,7 +8667,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9022,7 +8677,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9075,37 +8735,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119413573</v>
+        <v>119413593</v>
       </c>
       <c r="B66" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9118,10 +8773,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>528252</v>
+        <v>528309</v>
       </c>
       <c r="R66" t="n">
-        <v>7176983</v>
+        <v>7177102</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9153,7 +8808,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9163,12 +8818,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>på 2 levande sälgar</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9221,42 +8876,42 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119413593</v>
+        <v>119413550</v>
       </c>
       <c r="B67" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9264,10 +8919,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>528309</v>
+        <v>528017</v>
       </c>
       <c r="R67" t="n">
-        <v>7177102</v>
+        <v>7176978</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9299,7 +8954,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9309,12 +8964,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>gamla ringhack  död knäckt gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9323,34 +8978,8 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -9370,12 +8999,7 @@
         <v>119413555</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9492,15 +9116,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119413608</v>
+        <v>119413560</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9508,34 +9127,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ytter Rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>528412</v>
+        <v>528201</v>
       </c>
       <c r="R69" t="n">
-        <v>7177074</v>
+        <v>7177131</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9567,7 +9194,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9577,7 +9204,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9604,42 +9236,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119413574</v>
+        <v>119413565</v>
       </c>
       <c r="B70" t="n">
-        <v>79642</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9647,10 +9279,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>528251</v>
+        <v>528201</v>
       </c>
       <c r="R70" t="n">
-        <v>7176983</v>
+        <v>7177036</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9682,7 +9314,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9692,12 +9324,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>på 2 levande sälgar</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9706,34 +9338,8 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9747,6 +9353,366 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>119413592</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ytter Rissjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>528318</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7177094</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>119413596</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Ytter Rissjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>528271</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7177121</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>färska och gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>119413598</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Ytter Rissjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>528314</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7177133</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19331-2024 artfynd.xlsx
+++ b/artfynd/A 19331-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55773745</t>
         </is>
       </c>
     </row>
@@ -937,6 +947,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413536</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1078,6 +1093,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413540</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1219,6 +1239,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413543</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1360,6 +1385,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413547</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1501,6 +1531,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413563</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1642,6 +1677,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413564</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1783,6 +1823,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413566</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1924,6 +1969,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413569</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2060,6 +2110,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413572</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2201,6 +2256,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413573</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2342,6 +2402,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413577</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2483,6 +2548,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413580</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2624,6 +2694,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413582</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2765,6 +2840,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413584</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2906,6 +2986,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413587</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3047,6 +3132,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413589</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3188,6 +3278,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413590</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3329,6 +3424,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413594</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3436,6 +3536,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413537</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3548,6 +3653,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413539</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3655,6 +3765,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413544</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3762,6 +3877,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413545</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3869,6 +3989,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413546</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3976,6 +4101,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413549</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4083,6 +4213,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413556</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4190,6 +4325,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413558</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4297,6 +4437,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413559</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4404,6 +4549,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413567</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4511,6 +4661,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413570</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4618,6 +4773,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413575</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4725,6 +4885,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413576</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4837,6 +5002,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413579</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4944,6 +5114,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413583</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5051,6 +5226,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413591</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5158,6 +5338,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413595</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5265,6 +5450,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413597</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5372,6 +5562,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413599</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5479,6 +5674,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413601</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5586,6 +5786,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413603</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5693,6 +5898,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413605</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5800,6 +6010,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413606</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5907,6 +6122,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413608</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6014,6 +6234,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413609</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6121,6 +6346,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413611</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6262,6 +6492,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413541</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6403,6 +6638,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413552</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6544,6 +6784,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413562</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6685,6 +6930,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413578</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6826,6 +7076,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413586</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6967,6 +7222,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413574</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7108,6 +7368,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413535</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7249,6 +7514,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413538</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7390,6 +7660,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413542</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7531,6 +7806,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413551</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7667,6 +7947,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413553</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7808,6 +8093,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413554</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7949,6 +8239,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413557</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8090,6 +8385,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413561</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8202,6 +8502,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413568</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8309,6 +8614,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413571</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8450,6 +8760,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413581</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8591,6 +8906,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413585</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8732,6 +9052,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413588</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8873,6 +9198,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413593</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8993,6 +9323,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413550</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9113,6 +9448,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413555</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9233,6 +9573,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413560</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9353,6 +9698,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413565</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9473,6 +9823,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413592</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9593,6 +9948,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413596</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9713,8 +10073,87 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119413598</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>